--- a/output/2026-07_품목신고보고현황.xlsx
+++ b/output/2026-07_품목신고보고현황.xlsx
@@ -1602,7 +1602,6 @@
           <t>20260702</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>기타</t>
@@ -1739,7 +1738,6 @@
           <t>20260702</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>면역</t>
@@ -2017,7 +2015,6 @@
           <t>20260702</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>기타</t>
@@ -2295,7 +2292,6 @@
           <t>20260702</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>기타</t>
@@ -3301,77 +3297,77 @@
           <t>06월</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" s="7" t="n">
-        <v>0</v>
+      <c r="B8" s="9" t="n">
+        <v>53</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>106</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="O8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="S8" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="T8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" s="9" t="n">
+        <v>73</v>
+      </c>
+      <c r="V8" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="W8" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="X8" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="Y8" s="8" t="n">
-        <v>0</v>
+        <v>574</v>
       </c>
     </row>
     <row r="9">
@@ -4279,62 +4275,62 @@
           <t>06월</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="7" t="n">
-        <v>0</v>
+      <c r="B24" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>84</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>103</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I24" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="L24" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="M24" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="N24" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="O24" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="P24" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q24" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="R24" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="S24" s="9" t="n">
+        <v>1284</v>
       </c>
       <c r="T24" s="8" t="n">
-        <v>0</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="25">

--- a/output/2026-07_품목신고보고현황.xlsx
+++ b/output/2026-07_품목신고보고현황.xlsx
@@ -1602,6 +1602,7 @@
           <t>20260702</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>기타</t>
@@ -1738,6 +1739,7 @@
           <t>20260702</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>면역</t>
@@ -2015,6 +2017,7 @@
           <t>20260702</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>기타</t>
@@ -2292,6 +2295,7 @@
           <t>20260702</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>기타</t>
@@ -4276,43 +4280,43 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="G24" s="9" t="n">
         <v>7</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>18</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M24" s="9" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="O24" s="9" t="n">
         <v>13</v>
@@ -4324,10 +4328,10 @@
         <v>10</v>
       </c>
       <c r="R24" s="9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S24" s="9" t="n">
-        <v>1284</v>
+        <v>1334</v>
       </c>
       <c r="T24" s="8" t="n">
         <v>1948</v>

--- a/output/2026-07_품목신고보고현황.xlsx
+++ b/output/2026-07_품목신고보고현황.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="건강기능식품" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일반식품" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DASHBOARD" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="건강기능식품" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="일반식품" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="DASHBOARD" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -465,18 +465,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
@@ -1081,152 +1081,984 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>20130020008684</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>혜당명쾌정</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>(주)오투바이오</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>[마리골드꽃추출물] 노화로 인해 감소될 수 있는 황반색소밀도를 유지하여 눈 건강에 도움을 줄 수 있음
+[은행잎추출물] 기능성 내용 : 기억력 개선･혈행 개선에 도움을 줄 수 있음</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1일 2회, 1회 2정을 충분한 물과 함께 섭취.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>마리골드꽃추출물(고시형), 은행잎추출물(고시형), 스테아린산마그네슘, 이산화규소, 카복시메틸셀룰로스칼슘, 칼슘(고시형), 식물혼합분말, 타우린, 밀크씨슬추출물분말, 식물혼합분말, 유당, 결정셀룰로스, 비타민미네랄혼합분말, 비타민C, 구연산, 히드록시프로필메틸셀룰로스, 비타민E혼합제제, 글리세린지방산에스테르, 산화아연, 분말비타민A혼합제제</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>눈</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20230029284248</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>데일리 비오틴10000</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>(주)웰레스트</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>비오틴 (1) 지방, 탄수화물, 단백질 대사와 에너지 생성에 필요
+판토텐산 (1) 지방, 탄수화물, 단백질 대사와 에너지 생성에 필요</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1일1회, 1회 1정을 충분한 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>비오틴(고시형), 판토텐산칼슘(고시형), 기타가공품, 엘라스틴가수분해물, 폴리글리세린지방산에스테르, 이산화규소, 스테아린산마그네슘, 검정콩추출물분말, 히드록시프로필메틸셀룰로스, 생선콜라겐, 카복시메틸셀룰로스칼슘, 비타민C, 포도당, 효모식품</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>비타민</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2020001635485</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>키즈튼튼 글루콘산 아연</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>(주)유디바이오</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>[비타민C]
+(1) 결합조직 형성과 기능유지에 필요
+(2) 철의 흡수에 필요
+(3) 항산화 작용을 하여 유해산소로부터 세포를 보호하는데 필요
+[아연]
+(1) 정상적인 면역기능에 필요
+(2) 정상적인 세포분열에 필요</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 2정을 씹어서 섭취하십시오</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>비타민C, 글루콘산아연(고시형), 포도향분말, 사과향분말, 사과농축분말, 효소처리스테비아, 딸기농축액분말, 이산화규소, 스테아린산마그네슘, 딸기향분말, DL-사과산, 레드비트농축액, D-소비톨, 포도당, 과일채소혼합분말, 포도농축액분말, 아미노산혼합제제</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>비타민</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20230002296109</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>닥터디엣 컨트롤 다이렉트 다이어트(전량수출용)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>(주)신비바이오</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>[녹차 추출물] 항산화 ･ 체지방 감소 ･ 혈중 콜레스테롤 개선에 도움을 줄 수 있음
+[나이아신, 비타민B2] 체내 에너지 생성에 필요 
+[비타민B12] 정상적인 엽산 대사에 필요 
+[비타민B6] 단백질 및 아미노산 이용에 필요. 혈액의 호모시스테인 수준을 정상으로 유지하는데 필요 
+[판토텐산] 지방, 탄수화물, 단백질 대사와 에너지 생성에 필요 
+[아연] 정상적인 면역기능에 필요. 정상적인 세포분열에 필요 
+[비타민B1] 탄수화물과 에너지 대사에 필요</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>제조일로부터24개월</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1일 2회, 1회 2정을 충분한 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>비타민B1염산염, 비타민B2, 녹차추출물(고시형), 니코틴산아미드, 비타민B12, 혼합제제, 비타민B6염산염, 판토텐산칼슘, 산화아연, 스테아린산마그네슘, 타우린, 카복시메틸셀룰로스나트륨, L-카르니틴, 결정셀룰로스, 기타가공품, 알긴산, 엽산, 기타가공품, 히드록시프로필메틸셀룰로스, 이산화규소</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>비타민</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20230002296110</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>셀리나 녹차 카테킨 다이어트(전량수출용)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>(주)신비바이오</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>[녹차추출물] 항산화･체지방 감소･혈중 콜레스테롤 개선에 도움을 줄 수 있음
+[비타민B1] 탄수화물과 에너지 대사에 필요 
+[비타민B2] 체내 에너지 생성에 필요
+[판토텐산] 지방, 탄수화물, 단백질 대사와 에너지 생성에 필요</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1~3정을 충분한 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>판토텐산칼슘(고시형), 비타민 B2(고시형), 비타민 B1염산염(고시형), 녹차추출물분말(고시형), 과.채가공품, 레몬밤잎추출분말, 녹차추출물분말가루, 캐모마일추출물분말, 감태추출물분말, 신양벚나무열매추출분말, 이산화규소, 히드록시프로필메틸셀룰로스, 스테아린산마그네슘, 가교카복시메틸셀룰로스나트륨, 결정셀룰로스, 콜레우스포스콜리추출물, 핑거루트뿌리, 아프리카망고열매추출물분말</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>비타민</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>20230004624115</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>20260702</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>캡슐</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>20260702</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>비너스핏 라인</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>바이오디피씨(주)</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>[가르시니아캄보지아 추출물] 
 1) 탄수화물이 지방으로 합성되는 것을 억제하여 체지방 감소에 도움을 줄 수 있음</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>제조일로부터 2년까지</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>1일 2회, 1회 2캡슐을 충분한 물과 함께 섭취하십시오.</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>가르시니아캄보지아 추출물(고시형), 글리세린, 소르비탄지방산에스테르, 이산화티타늄, 정제수, 젤라틴, Clostridium butyricum strain Miyairi, 효모식품, 히드록시프로필메틸셀룰로스, 이산화규소, 스테아린산마그네슘, 이눌린/치커리추출물(고시형), 난소화성말토덱스트린(고시형), 혼합유당</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>다이어트</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>200400150832546</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>비타민D3 5000IU 미니</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>주식회사한미양행</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>[비타민D]
+(가) 칼슘과 인이 흡수되고 이용되는데 필요
+(나) 뼈의 형성과 유지에 필요
+(다) 골다공증발생 위험 감소에 도움을 줌</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월까지</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1캡슐을 충분한 물과 함께 섭취.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>비타민D3혼합제제, D-소비톨액, 글리세린, 젤라틴, 콩기름(대두유)</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>뼈건강</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>200400151101281</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>분말</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>비오베이비골드-우유맛(Biobaby gold milk flavor)(전량수출용)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>주)팜크로스</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>[프로바이오틱스]유산균 증식 및 유해균 억제･배변활동 원활･장 건강에 도움을 줄 수 있음</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>제조일로부터 36개월</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1포을 직접 또는 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>유산균혼합분말, 포도당, 비타민B6염산염, 비타민B1염산염, 산화아연, 니코틴산아미드, 이산화규소, 비타민C, 밀크향분말, 전지분유, 탈지분유, 덱스트린, 프락토올리고당, 식물성크림</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>프로바이오틱스</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20230002296108</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>닥터디엣 부기 다이렉트 칼륨(전량수출용)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>(주)신비바이오</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>(1) 체내 물과 전해질 균형에 필요</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>제조일로부터24개월</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1일 2회, 1회 2정을 충분한 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>칼륨(고시형), 덱스트린, 결정셀룰로스, 스테아린산, 은행잎추출물(고시형), 스테아린산마그네슘, 이산화규소, 치자청색소, 히드록시프로필메틸셀룰로스, 기타가공품, 기타가공품, 수산물가공품, 팥가루, 효모식품, 효소식품</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>비타민</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>200400200083439</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>액상</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>속편하게 프로</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>주식회사 노바렉스</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>[백편두추출분말(NOVAponin®)(제2024-6호)]
+(국문) 위 점막을 보호하여 위 건강에 도움을 줄 수 있음
+(영문) May help to maintain healthy stomach by protecting gastric mucosa
+[크롬] 체내 탄수화물, 지방, 단백질 대사에 관여
+[비타민 B6] 단백질 및 아미노산 이용에 필요, 혈액의 호모시스테인 수준을 정상으로 유지하는데 필요
+[비타민 B1] 탄수화물과 에너지 대사에 필요
+[비타민 B2] 체내 에너지 생성에 필요</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>제조일로부터 18개월</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1포를 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>크롬(고시형), 비타민 B6(고시형), 비타민 B1(고시형), 비타민 B2(고시형), 백편두추출분말(NOVAponinⓇ)(제2024-6호), 아미노산혼합분말, 아티초크추출분말, 타우린, 잔탄검, 황금혼합추출물, 효소처리스테비아, 혼합올리브유, 병풀추출, 감초추출물분말, 사과향, 정제수, 사과농축액, 식초분말, 시클로덱스트린액</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>비타민</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20140017002689</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>분말</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>프롬바이오 8종 코팅유산균</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>일동바이오사이언스(주)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>[프로바이오틱스 제품]①유산균 증식 및 유해균 억제에 도움을 줄 수 있음 ②배변활동 원활에 도움을 줄 수 있음 ③장건강에 도움을 줄 수 있음</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월까지</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>건강기능식품 원료로 사용</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Lactiplantibacillus plantarum(고시형), Streptococcus thermophilus(고시형), Bifidobacterium breve(고시형), Lacticaseibacillus casei(고시형), Lacticaseibacillus rhamnosus(고시형), Lactococcus lactis(고시형), Lacticaseibacillus rhamnosus(고시형), Bifidobacterium animalis ssp. lactis(고시형)</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>프로바이오틱스</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20140017002690</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>분말</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>스킨케어 SKIN CARE</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>일동바이오사이언스(주)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>[Lacticaseibacillus rhamnosus IDCC 3201 열처리배양건조물] 면역과민반응에 의한 피부상태 개선에 도움을 줄 수 있음
+[자일로올리고당(xylooligosaccharide) 분말(제2009-80호)] 장내 유익균 증식, 유해균 억제, 배변활동에 도움을 줄 수 있음
+[프로바이오틱스] ①유산균 증식 및 유해균 억제에 도움을 줄 수 있음 ②배변활동 원활에 도움을 줄 수 있음 ③장건강에 도움을 줄 수 있음</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>제조일로부터 18개월</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1포씩 직접 또는 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Enterococcus faecium(고시형), Lacticaseibacillus rhamnosus(고시형), Bifidobacterium bifidum(고시형), 락티카제이바실러스 람노서스 아이디씨씨3201 열처리배양건조물(제2018-12호), 자일로올리고당(xylooligosaccharide) 분말(기능성원료인정제2009-80호), 빌베리 추출물(고시형), 자일리톨, 에리스리톨, 기타가공품, 곡류가공품, 이산화규소, 기타가공품, 혼합제제, 과.채가공품, 탈지분유, 유산균혼합분말, 구연산(무수), 혼합제제</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>프로바이오틱스</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20230029284247</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>분말</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>인지력 두뇌엔 포스파티딜세린</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>(주)웰레스트</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>포스파티딜세린 ① 노화로 인해 저하된 인지력 개선·자외선에 의한 피부 손상으로부터 피부 건강 유지·피부보습에 도움을 줄 수 있음
+비타민E ① 항산화 작용을 하여 유해산소로부터 세포를 보호하는데 필요
+아연 ① 정상적인 면역기능에 필요 ② 정상적인 세포분열에 필요
+비타민D ①  칼슘과 인이 흡수되고 이용되는데 필요 ②  뼈의 형성과 유지에 필요  ③ 골다공증발생 위험 감소에 도움을 줌
+비타민K  ① 정상적인 혈액응고에 필요 ② 뼈의 구성에 필요</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1일 1회 1회 1포를 직접 또는 물과 함께 섭취하십시오</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>비타민 K1(고시형), 비타민 D3(고시형), 산화아연(고시형), 비타민 E(고시형), 포스파티딜세린(고시형), 기타가공품, 은행잎추출물분말, 이산화규소, 향료, 곡류가공품, 식물성크림, β-시클로덱스트린, 치커리추출물, 자일리톨</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>이너뷰티</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>200400200073422</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>뼈 건강 비타민D3 5000IU</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>(주)한국씨엔에스팜</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>[비타민D] 칼슘과 인이 흡수되고 이용되는데 필요 / 뼈의 형성과 유지에 필요 / 골다공증발생 위험 감소에 도움을 줌</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1캡슐을 충분한 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>비타민 D3 혼합제제유지, 젤라틴, 정제수, 글리세린, 콩기름(대두유)</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>뼈건강</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20130020024554</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>액상</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>에스클래스 BF-7 브레인 팩터 샷</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>(주)서흥헬스케어</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>피브로인추출물 BF-7(제2009-46호) : (국문) 기억력 개선에 도움을 줄 수 있음 (영문) May help to improve memory
+비타민B6 : (1) 단백질 및 아미노산 이용에 필요 (2) 혈액의 호모시스테인 수준을 정상으로 유지하는데 필요
+비타민B1 : 탄수화물과 에너지 대사에 필요</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>제조일로부터 18개월</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1병을 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>비타민B6염산염, 비타민 B1질산염(고시형), 피브로인추출물 BF-7(기능성원료인정제2009-46호), 정제수, 말티톨액, 프락토올리고당, 자몽농축액, 타우린, L-아르지닌, 자일리톨, 자몽향, 자몽향, 구연산, DL-사과산, 효소처리스테비아, 잔탄검, 변성전분, 황금혼합추출물, 유산균배양건조물, 아미노산혼합제제, 녹차추출물, 비타민B12혼합제제분말</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>두뇌</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>2024002023370</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>20260702</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>캡슐</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>20260702</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>눈건강 루테인 지아잔틴 아스타잔틴 골드</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>(주)비오팜2공장</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>[마리골드꽃추출물(지아잔틴함유)(제2026-9호)] (가)노화로 인해 감소될 수 있는 황반색소밀도를 유지하여 눈 건강에 도움을 줄 수 있음
 [헤마토코쿠스추출물] (가)눈의 피로도 개선에 도움을 줄 수 있음
 [비타민A] (가)어두운 곳에서 시각 적응을 위해 필요 (나)피부와 점막을 형성하고 기능을 유지하는데 필요 (다)상피세포의 성장과 발달에 필요</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>제조일로부터 24개월</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>1일 1회, 1회 1캡슐을 물과 함께 섭취하십시오.</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>헤마토코쿠스추출물(고시형), 비타민 A(고시형), 마리골드꽃추출물(지아잔틴함유)(제2026-9호), 젤라틴, 정제수, 글리세린, D-소비톨액, 카카오색소, 콩기름(대두유), 밀납, 레시틴</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>눈</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>20220011370441</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>20260702</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>분말</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>20260702</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>맥스 비타민C 3000 비타민D 3000</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>동서바이오팜(주) 안성공장</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>[비타민C]
 (1) 결합조직 형성과 기능유지에 필요
@@ -1238,24 +2070,1718 @@
 (3) 골다공증발생 위험 감소에 도움을 줌</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>제조일로부터 24개월</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>1일 1회, 1회 1포를 충분한 물과 함께 섭취하십시오</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>비타민 D 혼합제제, 비타민C</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>뼈건강</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>200400200062202</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>아이원 30 루테인지아잔틴 아스타잔틴 3012</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>(주)서흥</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>루테인지아잔틴추출복합물(제2025-35호) : (국문) 노화로 인해 감소될 수 있는 황반색소밀도를 유지하여 눈 건강에 도움을 줄 수 있음 (영문) May support eye health by maintaining the density of macular pigments which can be affected by aging
+헤마토코쿠스 추출물 : 눈의 피로도 개선에 도움을 줄 수 있음</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1캡슐을 충분한 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>헤마토코쿠스추출물(고시형), 루테인지아잔틴추출복합물(제2025-35호), 변성전분, 글리세린, 카라기난, D-소비톨액, 안나토색소, 카카오색소, 레몬오일</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>눈</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>200400200024099</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>젤리</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>더칼슘디키즈젤리</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>코스맥스바이오(주)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1) 비타민D : 칼슘과 인이 흡수되고 이용되는데 필요, 뼈의 형성과 유지에 필요, 골다공증 발생 위험 감소에 도움을 줌.
+2) 비타민K : 정상적인 혈액응고에 필요, 뼈의 구성에 필요.
+3) 칼슘 : 뼈와 치아 형성에 필요, 신경과 근육 기능 유지에 필요, 정상적인 혈액응고에 필요, 골다공증 발생 위험 감소에 도움을 줌.
+4) 마그네슘 : 에너지 이용에 필요, 신경과 근육 기능 유지에 필요.
+5) 망간 : 뼈 형성에 필요, 에너지 이용에 필요, 유해산소로부터 세포를 보호하는데 필요.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>제조일로부터 18개월.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1포(20g)를 씹어서 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>글루콘산마그네슘(고시형), 구연산칼슘(고시형), 비타민 K2(고시형), 황산망간(고시형), 비타민D3혼합제제, 정제수, 복사나무열매농축액, 프락토올리고당, 코코넛주스, 사과농축액, 로커스트콩검, 복숭아향, DL-사과산, 효소처리스테비아, 카라기난혼합제제</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>뼈건강</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>200400200073421</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>분말</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>미소젠-S</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>(주)한국씨엔에스팜</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>[포스파티딜세린] 노화로 인해 저하된 인지력개선･자외선에 의한 피부 손상으로부터 피부 건강 유지･피부보습에 도움을 줄 수 있음
+[테아닌] 스트레스로 인한 긴장완화에 도움을 줄 수 있음</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월까지</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1포를 충분한 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>포스파티딜세린(고시형), L-테아닌(고시형), 로즈마리추출물, α-시클로덱스트린, 치커리추출분말, 레몬과즙분말, 천연향료, 대나무수액, 사프란암술머리추출물분말</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>두뇌</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>202600031681</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>액상</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PDRN 뷰티 글로우 스틱 NMN 콤플렉스(전량수출용)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>신비바이오</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>[히알루론산] 피부보습에 도움을 줄 수 있음
+[비오틴] 지방, 탄수화물, 단백질 대사와 에너지 생성에 필요</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1포를 그대로 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>히알루론산, 비오틴, 자몽종자추출물, 우유단백질, 엘라스틴가수분해물, 비타민C혼합제제, 효모식품, 건조효모, 연어이리추출물, 젖산, 정제수, 오렌지농축액, 오렌지향, 효소처리스테비아, 생선콜라겐펩타이드, 기타가공품</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>이너뷰티</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20190009483878</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>하루틴 리포좀 멀티비타민 실버</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>우리바이오(주)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>[비타민 B1]
+탄수화물과 에너지 대사에 필요
+[비타민 B2]
+체내 에너지 생성에 필요
+[나이아신]
+체내 에너지 생성에 필요
+[판토텐산]
+지방, 탄수화물, 단백질 대사와 에너지 생성에 필요
+[비타민 B6]
+(가) 단백질 및 아미노산 이용에 필요
+(나) 혈액의 호모시스테인 수준을 정상으로 유지하는데 필요
+[엽산]
+(가) 세포와 혈액생성에 필요
+(나) 태아 신경관의 정상 발달에 필요
+(다) 혈액의 호모시스테인 수준을 정상으로 유지하는데 필요
+[비타민 B12]
+정상적인 엽산 대사에 필요
+[비오틴]
+지방, 탄수화물, 단백질 대사와 에너지 생성에 필요
+[비타민 C]
+(가) 결합조직 형성과 기능유지에 필요
+(나) 철의 흡수에 필요
+(다) 항산화 작용을 하여 유해산소로부터 세포를 보호하는데 필요
+[철]
+(가) 체내 산소운반과 혈액생성에 필요
+(나) 에너지 생성에 필요
+[아연]
+(가) 정상적인 면역기능에 필요
+(나) 정상적인 세포분열에 필요</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월까지</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1정을 충분한 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>혼합제제, 혼합제제, 해조칼슘, 결정셀룰로스, 덱스트린, 히드록시프로필메틸셀룰로스, 가교카복시메틸셀룰로스나트륨, 이산화규소, 스테아린산마그네슘, 글리세린지방산에스테르, 치자적색소, 유산균, 혼합제제, 이산화티타늄, 과.채가공품</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>멀티팩</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20190009483879</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>분말</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>올 케어 ll 24</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>우리바이오(주)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>[차전자피식이섬유]
+(가) 혈중 콜레스테롤 개선･배변활동 원활에 도움을 줄 수 있음</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1일 2회, 1회 1포를 충분한 물과 함께 섭취하십시오</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>차전자피식이섬유(고시형), 유산균혼합분말, 프락토올리고당, 아프리카망고씨앗추출물분말, 귀리식이섬유, 비타민미네랄혼합제제, 서양자두과즙분말, 수크랄로스, 자일리톨, 키위분말, 이산화규소, 이소말트, 구연산(무수), 키위향</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>장</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>200400170211975</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>분말</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>트루바이타민 D&amp;E</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>(주)비오팜</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>[비타민E] (1) 항산화 작용을 하여 유해산소로부터 세포를 보호하는데 필요
+[비타민D] (1)칼슘과 인이 흡수되고 이용되는데 필요 (2) 뼈의 형성과 유지에 필요 (3)골다공증발생 위험 감소에 도움을 줌</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1포를 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>비타민E혼합제제, 비타민D3혼합제제, 이산화규소, 효소처리스테비아, DL-사과산, 밀크향, 향료, 바나나향분말, 바나나엑기스분말, 자일리톨</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>뼈건강</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>200400200083440</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>혈당 앤 콜레</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>주식회사 노바렉스</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>[바나바잎 추출물] 식후 혈당상승 억제에 도움을 줄 수 있음
+[홍국] 혈중 콜레스테롤 개선에 도움을 줄 수 있음</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1SET (바나바잎추출물정제 700mg X 1T, 홍국정제 700mg X 1T)를 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>홍국(고시형), 바나바잎 추출물(고시형), 비타민 E(고시형), 혼합유당, 결정셀룰로스, 덱스트린, 칼슘(고시형), 히드록시프로필메틸셀룰로스, 스테아린산마그네슘(고시형), 이산화규소, 치자그린색소, 글리세린지방산에스테르혼합제제용액, 이산화티타늄, 치자청색소, 유단백가수분해물, 여주추출분말, 크롬(고시형), 산화아연(고시형), 비타민 B1(고시형), 밀크씨슬(카르두스 마리아누스) 추출물(고시형), 토마토농축분말, 비타민 D3(고시형), 비타민 K2(고시형)</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>혈당</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>200400150832547</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>피부보습 히알루론산</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>주식회사한미양행</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>[히알루론산]  
+피부보습･자외선에 의한 피부손상으로부터 피부건강 유지에 도움을 줄 수 있음
+[비타민A] 
+(가) 어두운 곳에서 시각 적응을 위해 필요
+(나) 피부와 점막을 형성하고 기능을 유지하는데 필요
+(다) 상피세포의 성장과 발달에 필요</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월까지</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 2캡슐 충분한 물과 함께 섭취.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>히알루론산(고시형), 비타민 A 혼합제제, 식용색소청색제1호, 식용색소황색제4호, 식용색소황색제5호, 식용색소적색제3호, 식용색소적색제2호, 식용색소적색제40호, 에틸바닐린, 이산화티타늄, D-소비톨액, 글리세린, 젤라틴, 콩기름(대두유), 생선콜라겐분말, 건조효모, 엘라스틴가수분해물, 레시틴, 밀납</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>이너뷰티</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>201200190071257</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>글루코 슬림핏 Cr</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>(주)한풍네이처팜</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>[녹차추출물] 항산화, 체지방 감소, 혈중 콜레스테롤 개선에 도움을 줄 수 있음
+[바나바잎추출물] 식후 혈당상승 억제에 도움을 줄 수 있음
+[크롬] 체내 탄수화물, 지방, 단백질 대사에 관여</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월까지</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 2정을 물과 함께 섭취하십시오</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>녹차추출물분말(고시형), 건조효모(크롬함유), 바나바잎 추출물(고시형), 결정셀룰로스, 해조칼슘, 히드록시프로필메틸셀룰로스, 스테아린산마그네슘, 카복시메틸셀룰로스칼슘, 이산화규소, 향료, 이산화티타늄, 글리세린지방산에스테르, 혼합제제, 구아바잎추출분말, 히비스커스꽃받침추출분말, 계피엑기스분말, 양배추추출액분말, 흰강낭콩추출분말, 블루베리농축분말, 구기자추출물분말, 블랙엘더베리추출물분말, 비타민미네랄혼합제제</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>혈당</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>200400170211974</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>원데이 멀티팩 더하기 비타민&amp;미네랄 19종</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>(주)비오팜</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>[칼슘] (가) 뼈와 치아 형성에 필요 (나) 신경과 근육 기능 유지에 필요 (다) 정상적인 혈액응고에 필요 (라) 골다공증 발생 위험 감소에 도움을 줌
+[마그네슘] (가) 에너지 이용에 필요 (나) 신경과 근육 기능 유지에 필요
+[비타민 C] (가)결합조직 형성과 기능유지에 필요 (나)철의 흡수에 필요 (다)항산화 작용을 하여 유해산소로부터 세포를 보호하는데 필요
+[철](가)체내 산소운반과 혈액생성에 필요, (나) 에너지 생성에 필요
+[비타민 E] 항산화 작용을 하여 유해산소로부터 세포를 보호하는데 필요
+[나이아신] (가)체내 에너지 생성에 필요
+[아연] (가)정상적인 면역기능에 필요 (나)정상적인 세포분열에 필요
+[망간](가)뼈 형성에 필요 (나)에너지 이용에 필요 (다)유해산소로부터 세포를 보호하는데 필요
+[비타민 A] (가)어두운 곳에서 시각 적응을 위해 필요 (나)피부와 점막을 형성하고 기능을 유지하는데 필요 (다)상피세포의 성장과 발달에 필요
+[판토텐산] (가)지방, 탄수화물, 단백질 대사와 에너지 생성에 필요 
+[셀레늄(또는 셀렌)] 유해산소로부터 세포를 보호하는데 필요
+[비타민 D] (가)칼슘과 인이 흡수되고 이용되는데 필요 (나)뼈의 형성과 유지에 필요 (다)골다공증발생 위험 감소에 도움을 줌
+[비타민 B12] (가)정상적인 엽산 대사에 필요
+[비타민 B6] (가)단백질 및 아미노산 이용에 필요 (나)혈액의 호모시스테인 수준을 정상으로 유지하는데 필요  
+[비타민 K] (가)정상적인 혈액응고에 필요 (나)뼈의 구성에 필요
+[비타민 B1] (가)탄수화물과 에너지 대사에 필요
+[비타민 B2] (가)체내 에너지 생성에 필요
+[엽산] (가)세포와 혈액생성에 필요 (나)태아 신경관의 정상 발달에 필요 (다)혈액의 호모시스테인 수준을 정상으로 유지하는데 필요
+[비오틴] (가)지방, 탄수화물, 단백질 대사와 에너지 생성에 필요</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1포(3제피정제)를 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>황산망간(고시형), 산화아연(고시형), 니코틴산아미드(고시형), 분말비타민A혼합제제, 판토텐산칼슘(고시형), 아셀렌산나트륨(고시형), 비타민D3혼합제제, 비오틴(고시형), 엽산(고시형), 비타민 B2(고시형), 비타민 B1염산염(고시형), 비타민K1혼합제제, 피리독신염산염(고시형), 분말비타민B12혼합제제, 탄산칼슘(고시형), 산화마그네슘(고시형), 비타민 C(고시형), 푸마르산제일철(고시형), 비타민E혼합제제, 해조칼슘, 스테아린산마그네슘, 이산화규소, 카복시메틸셀룰로스칼슘, 히드록시프로필메틸셀룰로스, 혼합유당, 덱스트린, 결정셀룰로스, 탄산칼슘혼합제제, 이산화티타늄, 치자황색소, 글리세린지방산에스테르, 홍국색소</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>멀티팩</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>200400170211973</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>브레인 시그널(전량수출용)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>(주)비오팜</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>[포스파티딜세린] (가)노화로 인해 저하된 인지력 개선 ･ 자외선에 의한 피부 손상으로부터 피부 건강 유지 ･ 피부보습에 도움을 줄 수 있음
+[은행잎 추출물] (가)기억력 개선 ･ 혈행 개선에 도움을 줄 수 있음
+[비타민E] (가)항산화 작용을 하여 유해산소로부터 세포를 보호하는데 필요</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 2캡슐을 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>비타민E혼합제제, 은행잎추출물(고시형), 포스파티딜세린(고시형), 이산화티타늄, 히드록시프로필메틸셀룰로스, 비타민D3혼합제제, 건조효모, 카복시메틸셀룰로스칼슘, 자당지방산에스테르, 이산화규소, 스테아린산마그네슘, 기타 수산물가공품, 기타가공품</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>두뇌</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>200600200033263</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>액상</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Drinkable Hyaluronic Acid</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>콜마비앤에이치(주)음성공장</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>- 히알루론산 : 피부보습에 도움을 줄 수 있음</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>제조일로부터 18개월</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1포(20mL)를 직접 또는 물에 타서 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>히알루론산(고시형), 사과농축액, DL-사과산, 사과향, 에리스리톨, 정제수, 수크랄로스, 엘라스틴가수분해물, 우유단백</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>이너뷰티</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>200600200033262</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>젤리</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>석류미인(인도)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>콜마비앤에이치(주)음성공장</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>- 갱년기 여성의 건강에 도움을 줄 수 있음
+- 피부보습에 도움을 줄 수 있음
+- 자외선으로 인한 피부 손상으로부터 피부건강을 유지하는데 도움을 줄 수 있음</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>제조일로부터 18개월</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1일 2회, 1회 1포(15g)를 씹어서 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>석류농축액(기능성원료인정제2014-22호), 젤란검, 한천, 스테비올배당체, 아미드펙틴, 혼합제제, 젖산칼슘, 구연산삼나트륨, 로커스트콩검, 잔탄검, 딸기농축액, 망고농축액, 파인애플농축액, 난소화성말토덱스트린(고시형), 이소말토올리고당, 정제수</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>여성건강</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20240028080581</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>분말</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Pineapple Enzyme Melt</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>콜마비앤에이치(주)세종3공장</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>- 비타민 B1 : 탄수화물과 에너지 대사에 필요
+- 판토텐산 : 지방, 탄수화물, 단백질 대사와 에너지 생성에 필요
+- 비오틴 : 지방, 탄수화물, 단백질 대사와 에너지 생성에 필요</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1포를 그대로 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>비오틴, 비타민 B1염산염(고시형), 판토텐산칼슘(고시형), 스테비올배당체, 효소혼합분말, 이산화규소, 쌀가루, 폴리덱스트로스, 에리스리톨, 덱스트린, 동결건조파인애플분말, 프로테아제, DL-사과산, 제삼인산칼슘, 파파야추출분말</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>비타민</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20230029284249</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>파낙샘</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>(주)웰레스트</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>(1) 정상적인 면역기능에 필요
+(2) 정상적인 세포분열에 필요</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1캡슐을 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>산화아연(고시형), 젤라틴, 정제수, 자당지방산에스테르, 기타가공품, 히드록시프로필메틸셀룰로스</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>비타민</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20130020024555</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>셀레온 미토밸런스</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>(주)서흥헬스케어</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>코엔자임Q10 : 항산화∙높은 혈압 감소에 도움을 줄 수 있음
+헤마토코쿠스 추출물 : 눈의 피로도 개선에 도움을 줄 수 있음
+셀레늄 : 유해산소로부터 세포를 보호하는데 필요
+마리골드꽃추출물 : 노화로 인해 감소될 수 있는 황반색소밀도를 유지하여 눈건강에 도움을 줄 수 있음
+나이아신 : 체내 에너지 생성에 필요
+비타민B12 : 정상적인 엽산 대사에 필요
+판토텐산 : 지방, 탄수화물, 단백질 대사와 에너지 생성에 필요
+비타민B1 : 탄수화물과 에너지 대사에 필요
+비타민B2 : 체내 에너지 생성에 필요
+비오틴 : 지방, 탄수화물, 단백질 대사와 에너지 생성에 필요
+비타민B6 : (1) 단백질 및 아미노산 이용에 필요 (2) 혈액의 호모시스테인 수준을 정상으로 유지하는데 필요
+아연 : (1) 정상적인 면역기능에 필요 (2) 정상적인 세포분열에 필요
+비타민D : (1) 칼슘과 인이 흡수되고 이용되는데 필요 (2) 뼈의 형성과 유지에 필요 (3) 골다공증발생 위험 감소에 도움을 줌
+엽산 : (1) 세포와 혈액생성에 필요 (2) 태아 신경관의 정상 발달에 필요 (3) 혈액의 호모시스테인 수준을 정상으로 유지하는데 필요</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1포를 충분한 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>건조효모(셀렌함유), 헤마토코쿠스추출물(고시형), 니코틴산아미드(고시형), 비타민B12혼합제제분말, 판토텐산칼슘(고시형), 비타민 B1질산염(고시형), 비타민 B2(고시형), 비오틴 혼합분말, 비타민B6염산염, 산화아연(고시형), 비타민 D3 혼합제제유지, 엽산(고시형), 마리골드꽃추출물(고시형), 코엔자임Q10(고시형), 젤라틴, 글리세린, D-소비톨액, 카카오색소, 안나토색소, 콩기름(대두유), 결정셀룰로스, 혼합유당, 밀납, 해조칼슘, 가교카복시메틸셀룰로스나트륨, 히드록시프로필메틸셀룰로스, 레시틴, 스테아린산마그네슘(고시형), 이산화규소, 이산화티타늄, 글리세린지방산에스테르, 카카오색소</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>눈</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>200400170211972</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>프리미엄 혈당케어</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>(주)비오팜</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>[바나바잎추출물] 식후 혈당상승 억제에 도움을 줄 수 있음</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1정을 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>바나바잎 추출물(고시형), 혼합유당, 결정셀룰로스, 이산화티타늄, 스테아린산마그네슘, 이산화규소, 히드록시프로필메틸셀룰로스, 해조칼슘, 글리세린지방산에스테르, 가교카복시메틸셀룰로스나트륨</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>혈당</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>201200190071255</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>바나바잎 추출물 크롬 200 µg</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>(주)한풍네이처팜</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>[바나바잎추출물]: 식후 혈당상승 억제에 도움을 줄 수 있음
+[크롬]: 체내 탄수화물, 지방, 단백질 대사에 관여
+[아연]: 정상적인 면역기능에 필요, 정상적인 세포분열에 필요
+[셀렌]: 유해산소로부터 세포를 보호하는데 필요
+[비타민B12] 정상적인 엽산 대사에 필요
+[비타민B6]: 단백질 및 아미노산 이용에 필요, 혈액의 호모시스테인 수준을 정상으로 유지하는데 필요
+[엽산]: 세포와 혈액생성에 필요, 태아 신경관의 정상 발달에 필요, 혈액의 호모시스테인 수준을 정상으로 유지하는데 필요</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월까지</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1정을 물과 함께 섭취하십시오</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>바나바잎추출물, 건조효모(크롬함유), 산화아연, 아셀렌산나트륨, 비타민B12, 혼합제제, 비타민B6염산염, 엽산, 참당귀추출분말, 난소화성말토덱스트린(고시형), 유청칼슘, 결정셀룰로스, 혼합제제, 맥주효모추출물, 아라비아검, 대나무수액, 유채경화유, 호로파종자(고시형), 산화마그네슘, 여주추출분말, 키토올리고당분말(고시형), 쉘락, 비타민C, 카나우바왁스, 코엔자임Q10(고시형), 건조효모, 비오틴 혼합분말, 건조효모</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>혈당</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20160006007139</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>식후 걱정엔</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>(주)종근당바이오</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>(국문) 식후 혈중 중성지방 개선에 도움을 줄 수 있음
+(영문) May help to maintain healthy blood triglyceride level</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>24개월</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1캡슐을 물과 함께 섭취</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Lactiplantibacillus plantarum Q180(제2021-23호), 젤라틴, 프탈산히드록시프로필메틸셀룰로스, 이산화티타늄, 갈락토올리고당, 스테아린산마그네슘, 밀식이섬유(고시형), 난소화성말토덱스트린분말(고시형), 프락토올리고당(고시형), 쌀발효분말</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>다이어트</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>200400200083441</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>관절혈통</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>주식회사 노바렉스</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>[은행잎 추출물] 기억력 개선·혈행 개선에 도움을 줄 수 있음
+[홍국] 혈중 콜레스테롤 개선에 도움을 줄 수 있음
+[바나바잎 추출물] 식후 혈당상승 억제에 도움을 줄 수 있음
+[아연] 정상적인 면역기능에 필요, 정상적인 세포분열에 필요
+[망간] 뼈 형성에 필요, 에너지 이용에 필요, 유해산소로부터 세포를 보호하는데 필요
+[셀레늄] 유해산소로부터 세포를 보호하는데 필요
+[비타민 D] 칼슘과 인이 흡수되고 이용되는데 필요, 뼈의 형성과 유지에 필요, 골다공증발생 위험 감소에 도움을 줌
+[비타민 K] 정상적인 혈액응고에 필요, 뼈의 구성에 필요
+[크릴오일등복합물(FlexPro MD®)(제2022-39호)]
+(국문) 관절건강에 도움을 줄 수 있음
+(영문) May help to maintain healthy joint</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1포(1포 : 은행잎정제 300mg X 1T, 비타민미네랄정제 300mg X 1T, 연질캡슐 600mg X 1C)를 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>은행잎추출물(고시형), 홍국(고시형), 산화아연(고시형), 황산망간(고시형), 아셀렌산나트륨(고시형), 비타민 D3(고시형), 바나바잎 추출물(고시형), 비타민 K1(고시형), 크릴오일등복합물(FlexPro MDⓇ)(제2022-39호), 젤라틴, 글리세린, D-소비톨액, 카카오색소, 결정셀룰로스, 콩기름(대두유), 혼합유당, 칼슘(고시형), 히드록시프로필메틸셀룰로스, 가교카복시메틸셀룰로스나트륨, 스테아린산마그네슘(고시형), 이산화티타늄, 이산화규소, 글리세린지방산에스테르혼합제제용액, 카카오색소, 카라멜색소 Ⅳ, 귀리식이섬유(고시형), 차전자피식이섬유(고시형), 여주추출분말, 뽕나무잎추출분말, 난소화성말토덱스트린(고시형), 생강추출분말, 참당귀추출분말, 홍삼농축액(고시형), 옥타코사놀 함유 유지(고시형), 코엔자임Q10(고시형), 병풀추출, 과일혼합분말, 혼합야채분말, 엠에스엠(고시형), NAG(엔에이지, N-아세틸글루코사민, N-Acetylglucosamine)(고시형), 초록입홍합분말, 보스웰리아추출물분말, 강황추출물분말, 로즈힙추출물분말, 생선콜라겐</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>혈당</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>200400200142178</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>광동관절케어글루코사민맥스</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>광동헬스바이오(주) 2공장</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>[글루코사민]
+(가) 관절 및 연골 건강에 도움을 줄 수 있음
+[비타민C]
+(가) 결합조직 형성과 기능유지에 필요
+(나) 철의 흡수에 필요
+(다) 항산화 작용을 하여 유해산소로부터 세포를 보호하는데 필요
+[아연]
+(가) 정상적인 면역기능에 필요
+(나) 정상적인 세포분열에 필요
+[비타민D]
+(가) 칼슘과 인이 흡수되고 이용되는데 필요
+(나) 뼈의 형성과 유지에 필요
+(다) 골다공증발생 위험 감소에 도움을 줌
+[비타민B6]
+(가) 단백질 및 아미노산 이용에 필요
+(나) 혈액의 호모시스테인 수준을 정상으로 유지하는데 필요
+[비타민B1]
+(가) 탄수화물과 에너지 대사에 필요</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 2정을 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>비타민 C(고시형), 글루코사민(고시형), 산화아연(고시형), 비타민 D3(고시형), 비타민 B6(고시형), 비타민 B1염산염(고시형), 결정셀룰로스, 히드록시프로필메틸셀룰로스, 이산화규소, 스테아린산마그네슘, 글리세린지방산에스테르, 생선콜라겐, 다미아나잎추출분말, 엘라스틴가수분해물, 굴껍질분말, 상어연골분말, 초록입홍합분말, 보스웰리아분말, 엠에스엠(고시형)</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>관절</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>201200190071256</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>액상</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>키드큐 금동보감</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>(주)한풍네이처팜</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>[홍삼] 면역력 증진, 피로개선, 혈소판 응집억제를 통한 혈액흐름, 기억력개선, 항산화에 도움을 줄수 있음</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월까지</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1포를 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>홍삼농축액, 잔탄검, 황금혼합추출물, 감초농축액, 구연산(무수), 복령농축액, 정제수, 지황농축액, 벌꿀, 배농축액, 프락토올리고당, 글리신, 시클로덱스트린, 맥문동추출물, 요구르트향분말, 나한과추출물분말</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>홍삼</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>200400200142179</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>VitaminK2(100 MCG)+VitaminD3(전량수출용)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>광동헬스바이오(주) 2공장</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>[비타민K]
+(1) 정상적인 혈액응고에 필요
+(2) 뼈의 구성에 필요
+[비타민D]
+(1) 칼슘과 인이 흡수되고 이용되는데 필요
+(2) 뼈의 형성과 유지에 필요
+(3) 골다공증발생 위험 감소에 도움을 줌</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>제조일로부터 36개월</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1캡슐을 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>비타민 K2(고시형), 비타민 D3(고시형), 젤라틴, 글리세린, D-소비톨액, 카라멜색소 Ⅳ, 해바라기유</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>뼈건강</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>200400200083442</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>올인원 뉴트리션 멀티비타민 원팩</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>주식회사 노바렉스</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>[EPA 및 DHA 함유 유지] 혈중 중성지질 개선·혈행 개선에 도움을 줄 수 있음, 건조한 눈을 개선하여 눈 건강에 도움을 줄 수 있음
+[마리골드꽃추출물] 노화로 인해 감소될 수 있는 황반색소밀도를 유지하여 눈 건강에 도움을 줄 수 있음
+[비타민 E] 항산화 작용을 하여 유해산소로부터 세포를 보호하는데 필요
+[비타민 A] 어두운 곳에서 시각 적응을 위해 필요, 피부와 점막을 형성하고 기능을 유지하는데 필요, 상피세포의 성장과 발달에 필요
+[베타카로틴] 어두운 곳에서 시각 적응을 위해 필요, 피부와 점막을 형성하고 기능을 유지하는데 필요, 상피세포의 성장과 발달에 필요
+[비타민 D] 칼슘과 인이 흡수되고 이용되는데 필요, 뼈의 형성과 유지에 필요, 골다공증발생 위험 감소에 도움을 줌
+[비타민 C] 결합조직 형성과 기능유지에 필요, 철의 흡수에 필요, 항산화 작용을 하여 유해산소로부터 세포를 보호하는데 필요
+[망간] 뼈 형성에 필요, 에너지 이용에 필요, 유해산소로부터 세포를 보호하는데 필요
+[철] 체내 산소운반과 혈액생성에 필요, 에너지 생성에 필요
+[비타민 B12] 정상적인 엽산 대사에 필요
+[비타민 B6] 단백질 및 아미노산 이용에 필요, 혈액의 호모시스테인 수준을 정상으로 유지하는데 필요
+[비타민 B1] 탄수화물과 에너지 대사에 필요
+[비타민 B2] 체내 에너지 생성에 필요
+[나이아신] 체내 에너지 생성에 필요
+[몰리브덴] 산화·환원 효소의 활성에 필요
+[크롬] 체내 탄수화물, 지방, 단백질 대사에 관여
+[아연] 정상적인 면역기능에 필요, 정상적인 세포분열에 필요
+[판토텐산] 지방, 탄수화물, 단백질 대사와 에너지 생성에 필요
+[셀레늄] 유해산소로부터 세포를 보호하는데 필요
+[구리] 철의 운반과 이용에 필요, 유해산소로부터 세포를 보호하는데 필요
+[비타민 K] 정상적인 혈액응고에 필요, 뼈의 구성에 필요
+[엽산] 세포와 혈액생성에 필요, 태아 신경관의 정상 발달에 필요, 혈액의 호모시스테인 수준을 정상으로 유지하는데 필요
+[요오드] 갑상선 호르몬의 합성에 필요, 에너지 생성에 필요, 신경발달에 필요
+[비오틴] 지방, 탄수화물, 단백질 대사와 에너지 생성에 필요
+[밀크씨슬(카르두스 마리아누스) 추출물] 간 건강에 도움을 줄 수 있음
+[마그네슘] 에너지 이용에 필요, 신경과 근육 기능 유지에 필요</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1포(1포 : 연질캡슐 600mg X 2C, 비타민미네랄정제 600mg X 1T, 밀크씨슬정제 750mg X 1T)를 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>크롬(고시형), 몰리브덴(고시형), 니코틴산아미드(고시형), EPA 및 DHA 함유 유지(고시형), 밀크씨슬(카르두스 마리아누스) 추출물(고시형), 산화마그네슘(고시형), 비타민 C(고시형), 마리골드꽃추출물(고시형), 망간(고시형), 푸마르산제일철(고시형), 비타민 B12(고시형), 비타민 B6(고시형), 비타민 B1(고시형), 비타민 B2(고시형), 비타민 E(고시형), 스테아린산마그네슘(고시형), 산화아연(고시형), 판토텐산칼슘(고시형), 아셀렌산나트륨(고시형), 황산동(고시형), 비타민 A(고시형), 비타민 K1(고시형), 베타카로틴(고시형), 비타민 D3(고시형), 엽산(고시형), 요오드칼륨(고시형), 비오틴(고시형), 젤라틴, 글리세린, D-소비톨액, 안나토색소, 결정셀룰로스, 결정셀룰로스, 밀납(백납), 칼슘(고시형), 칼슘(고시형), 히드록시프로필메틸셀룰로스, 가교카복시메틸셀룰로스나트륨, 스테아린산마그네슘(고시형), 이산화규소, 레시틴, 이산화티타늄, 글리세린지방산에스테르혼합제제용액, 카민, 치자황색소, 카라멜색소 Ⅳ</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>멀티팩</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>200400200073423</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>마이핏 V 코큐텐 코엔자임Q10</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>(주)한국씨엔에스팜</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>[코엔자임Q10] 항산화･높은 혈압 감소에 도움을 줄 수 있음
+[비타민B1] 탄수화물과 에너지 대사에 필요
+[비타민B2] 체내 에너지 생성에 필요
+[비타민C] 결합조직 형성과 기능유지에 필요, 철의 흡수에 필요, 항산화 작용을 하여 유해산소로부터 세포를 보호하는데 필요
+[비타민E] 항산화 작용을 하여 유해산소로부터 세포를 보호하는데 필요
+[셀렌] 유해산소로부터 세포를 보호하는데 필요
+[아연] 정상적인 면역기능에 필요, 정상적인 세포분열에 필요
+[엽산] 세포와 혈액생성에 필요, 태아 신경관의 정상 발달에 필요, 혈액의 호모시스테인 수준을 정상으로 유지하는데 필요</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>24개월</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1캡슐을 충분한 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>비타민 B2(고시형), 비타민 B1염산염(고시형), 코엔자임Q10(고시형), 비타민 C(고시형), 비타민 E(고시형), 산화아연(고시형), 아셀렌산나트륨(고시형), 엽산(고시형), 젤라틴, 정제수, 글리세린, 홍국색소, 이산화티타늄, 치자청색소, 치자황색소, 콩기름(대두유), 밀납(백납), 레시틴, 효모추출물, 녹차추출물(고시형), 프로폴리스추출물(고시형), 히알루론산(고시형), 엘라스틴가수분해물, 건조효모, 세븐베리농축분말, 비오틴</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>항산화</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>201200190071258</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>The 명품 프리미엄 파인(Fine) OK</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>(주)한풍네이처팜</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>[비타민E] 항산화 작용을 하여 유해산소로부터 세포를 보호하는데 필요</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월까지</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1일 2회, 1회 1캡슐을 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>d-α-토코페롤, 젤라틴, 아미드펙틴, 글리세린, 정제수, 기타가공품</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>비타민</t>
         </is>
       </c>
     </row>
@@ -1270,18 +3796,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1569,7 +4095,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20060415215381</t>
+          <t>19990443207148</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1579,30 +4105,34 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20060415215</t>
+          <t>19990443207</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>레몬샷앰플</t>
+          <t>솔티카라멜L</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>과.채주스</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>주식회사 노바렉스 2공장</t>
+          <t>(주)세전</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20260702</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>물엿, 설탕, 기타과당, 정제수, 가공유지, 덱스트린, 포도당, 버터, 당류가공품, 혼합분유, 유청, 혼합제제, 당류가공품, 변성전분, 정제소금, 향료제제, 글리세린지방산에스테르, 소르비탄지방산에스테르, 카라기난, 소브산칼륨, 아라비아검, 잔탄검</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>기타</t>
@@ -1612,7 +4142,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>200703553072008</t>
+          <t>200004613259346</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1622,32 +4152,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>20070355307</t>
+          <t>20000461325</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>노티드 가을학기</t>
+          <t>GM믹스67</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>(주)토스크</t>
+          <t>(주) 삼지에프 에스</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260704</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>식용색소적색제40호알루미늄레이크, 식용색소황색제4호알루미늄레이크, 코치닐추출색소, 식용색소청색제1호알루미늄레이크, 혼합제제, 가공유지, 코코아분말, 이산화티타늄, 당류가공품</t>
+          <t>생강가루, 변성전분, 옥수수전분, 팽창제제, 정제소금</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1659,7 +4189,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20100347108249</t>
+          <t>20010306231326</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1669,32 +4199,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20100347108</t>
+          <t>20010306231</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>포크향분말</t>
+          <t>캔디과립</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>캔디류</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>(주)지앤씨에프에스</t>
+          <t>(주)에스엘에스</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>혼합제제, 덱스트린</t>
+          <t>홍화황색소, 물엿, 구연산, 향료, 기타설탕, DL-사과산, 정제수</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1706,7 +4236,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20110402172414</t>
+          <t>20060415215381</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1716,40 +4246,44 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20110402172</t>
+          <t>20060415215</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>우진신바이오틱스 평창표고버섯기루</t>
+          <t>레몬샷앰플</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>과.채주스</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>농업회사법인 린디미방 주식회사</t>
+          <t>주식회사 노바렉스 2공장</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20260702</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>야채혼합농축분말, 황금혼합추출물, 레몬주스, 오렌지착즙액, 사과착즙액, 건조효모, 건조효모, 건조효모, 기타소금</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>면역</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2012020000248</t>
+          <t>200703553072008</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1759,22 +4293,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>20120200002</t>
+          <t>20070355307</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KH발효혼합분말</t>
+          <t>노티드 가을학기</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>(주)진향</t>
+          <t>(주)토스크</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1784,7 +4318,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>기타가공품, 기타가공품, 기타가공품</t>
+          <t>식용색소적색제40호알루미늄레이크, 식용색소황색제4호알루미늄레이크, 코치닐추출색소, 식용색소청색제1호알루미늄레이크, 혼합제제, 가공유지, 코코아분말, 이산화티타늄, 당류가공품</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1796,7 +4330,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>201504612251561</t>
+          <t>20080320042160</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1806,44 +4340,44 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20150461225</t>
+          <t>20080320042</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>장미분말</t>
+          <t>프로넛 무설탕 젤리 사과향</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>캔디류</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>해찬솔푸드</t>
+          <t>팜드림(주)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>덱스트린, 장미추출액</t>
+          <t>향료, 구연산, 비타민C, 기타가공품, 홍화황색소, 혼합제제, 정제수, 자일리톨</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>구강</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20150569083192</t>
+          <t>20080320042161</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1853,44 +4387,44 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20150569083</t>
+          <t>20080320042</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>냉동골드키위</t>
+          <t>프로넛 무설탕 젤리 레몬향</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>캔디류</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>농업회사법인 주식회사 지엔에프앤비 2공장</t>
+          <t>팜드림(주)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>키위열매</t>
+          <t>향료, 구연산, 비타민C, 기타가공품, 홍화황색소, 혼합제제, 정제수, 자일리톨</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>구강</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20160570162325</t>
+          <t>20080320042162</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1900,44 +4434,44 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20160570162</t>
+          <t>20080320042</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>육류 염지파우더</t>
+          <t>프로넛 무설탕 젤리 샤인머스켓향</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>캔디류</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MJ 푸드</t>
+          <t>팜드림(주)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>천연향신료, 가공소금</t>
+          <t>향료, 구연산, 비타민C, 기타가공품, 타르색소제제, 혼합제제, 정제수, 자일리톨</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>구강</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20170614111831</t>
+          <t>20100347108249</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1947,12 +4481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20170614111</t>
+          <t>20100347108</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>이지핏 이너글로우 업 콜라겐 PDRN</t>
+          <t>포크향분말</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1962,7 +4496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>(주)엔트리</t>
+          <t>(주)지앤씨에프에스</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1972,19 +4506,19 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>히알루론산, 기타가공품, DL-사과산, 구연산, 효모추출물, 기타가공품, 기타가공품, 효소처리스테비아, 향료, 혼합제제, 기타가공품, 과.채가공품, 과.채가공품, 기타과당, 정제수</t>
+          <t>혼합제제, 덱스트린</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20170415060116</t>
+          <t>2011055509651</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1994,30 +4528,34 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20170415060</t>
+          <t>20110555096</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>알룰로스 복숭아화채</t>
+          <t>통째로 갈아만든 ABCL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>과.채주스</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>(주)호재준</t>
+          <t>경북햇살농원 영농조합법인</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20260702</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>사과, 당근, 비트레드, 비타민C, 레몬농축액</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>기타</t>
@@ -2027,7 +4565,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2017051225027</t>
+          <t>20110402172414</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2037,44 +4575,44 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>20170512250</t>
+          <t>20110402172</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>황칠추출분말</t>
+          <t>우진신바이오틱스 평창표고버섯기루</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>농업회사법인 주식회사 다고</t>
+          <t>농업회사법인 린디미방 주식회사</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>황칠나무</t>
+          <t>표고버섯가루</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>면역</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20170435483109</t>
+          <t>2012020000248</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2084,22 +4622,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20170435483</t>
+          <t>20120200002</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>모닝 36 타임</t>
+          <t>KH발효혼합분말</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>농업회사법인 넉넉한사람들(주)</t>
+          <t>(주)진향</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2109,7 +4647,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>눈꽃동충하초추출액, 헛개나무열매추출액, 구기자농축액, 대추농축액, 기타올리고당, 구연산삼나트륨, 정제수</t>
+          <t>기타가공품, 기타가공품, 기타가공품</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2121,7 +4659,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2018042401069</t>
+          <t>2013022708455</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2131,12 +4669,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20180424010</t>
+          <t>20130227084</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>클리어 맥(Clear MAC)</t>
+          <t>다시마육수</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2146,29 +4684,29 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>(주)서흥헬스케어 2공장</t>
+          <t>새벽팜 1공장</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>차전자피식이섬유(고시형), 난소화성말토덱스트린(고시형), 이눌린/치커리추출물(고시형), 구아검가수분해물(고시형), 펙틴</t>
+          <t>정제수, 건조명태머리, 건조멸치, 건보리새우, 건표고버섯, 건조다시마, 무</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>면역</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20190391582682</t>
+          <t>201504612251561</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2178,22 +4716,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>20190391582</t>
+          <t>20150461225</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>레드비트 농축액</t>
+          <t>장미분말</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>(주)네추럴웨이 포천제2공장</t>
+          <t>해찬솔푸드</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2203,7 +4741,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>구연산(무수), 레드비트농축액</t>
+          <t>덱스트린, 장미추출액</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2215,7 +4753,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2020039310948</t>
+          <t>20150569083192</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2225,22 +4763,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>20200393109</t>
+          <t>20150569083</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>시원하게 마시는 도라지차</t>
+          <t>냉동골드키위</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>여주시 농업기술센터 농산물종합가공센터</t>
+          <t>농업회사법인 주식회사 지엔에프앤비 2공장</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2250,19 +4788,19 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>도라지뿌리, 둥굴레뿌리, 정제수</t>
+          <t>키위열매</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>면역</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2020042006896</t>
+          <t>20160570162325</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2272,12 +4810,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>20200420068</t>
+          <t>20160570162</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>락토바실러스 플란타룸 LRCC 5193</t>
+          <t>육류 염지파우더</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2287,7 +4825,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>주식회사 아이제이푸드</t>
+          <t>MJ 푸드</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2295,7 +4833,11 @@
           <t>20260702</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>천연향신료, 가공소금</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>기타</t>
@@ -2305,7 +4847,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20200391559462</t>
+          <t>20170347016347</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2315,32 +4857,32 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>20200391559</t>
+          <t>20170347016</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>파바빈프로테인</t>
+          <t>카페게이트 홍차라떼 파우더</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>(주)성진바이오 제1공장</t>
+          <t>(주)베오베</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260704</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>해바라기씨앗, 잠두씨앗</t>
+          <t>설탕, 혼합분유, 덱스트린, 고형차, 혼합제제, 혼합제제, 제삼인산칼슘</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2352,7 +4894,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2020053007624</t>
+          <t>20170614111831</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2362,22 +4904,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>20200530076</t>
+          <t>20170614111</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>흑하랑상추복합발효추출물</t>
+          <t>이지핏 이너글로우 업 콜라겐 PDRN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>농업회사법인주식회사유일식품</t>
+          <t>(주)엔트리</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2387,19 +4929,19 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>건조상추, 정제수, 쌀, 강황뿌리줄기, 보리</t>
+          <t>히알루론산, 기타가공품, DL-사과산, 구연산, 효모추출물, 기타가공품, 기타가공품, 효소처리스테비아, 향료, 혼합제제, 기타가공품, 과.채가공품, 과.채가공품, 기타과당, 정제수</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>피부</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2021029327894</t>
+          <t>20170415060116</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2409,32 +4951,32 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>20210293278</t>
+          <t>20170415060</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>레인보우 미니구슬 푸드컬러 S</t>
+          <t>알룰로스 복숭아화채</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>내츄럴팩토리 주식회사</t>
+          <t>(주)호재준</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>캔디류, 가공유지, 치자청색소, 식품첨가물혼합제제, 식품첨가물혼합제제, 치자황색소, 식품첨가물혼합제제, 베리류색소, 식품첨가물</t>
+          <t>알룰로오스, 백포도농축과즙, 복사나무열매, 오렌지농축주스, 백포도과즙</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2446,7 +4988,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>202206834731187</t>
+          <t>2017051225027</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2456,12 +4998,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>20220683473</t>
+          <t>20170512250</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>소연골 콘드로이친 1200 트리플</t>
+          <t>황칠추출분말</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2471,7 +5013,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>주식회사 에이브바이오랩스</t>
+          <t>농업회사법인 주식회사 다고</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2481,19 +5023,19 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>고형차, 식품첨가물</t>
+          <t>황칠나무</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>관절</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2023052806085</t>
+          <t>20170435483109</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2503,32 +5045,32 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>20230528060</t>
+          <t>20170435483</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>참송이버섯 분말</t>
+          <t>모닝 36 타임</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>포천시농산물종합가공센터</t>
+          <t>농업회사법인 넉넉한사람들(주)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260704</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>송이자실체</t>
+          <t>눈꽃동충하초추출액, 헛개나무열매농축액, 구기자농축액, 대추농축액, 기타올리고당, 구연산삼나트륨, 정제수</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2540,7 +5082,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20230528144330</t>
+          <t>2018042401069</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2550,12 +5092,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>20230528144</t>
+          <t>20180424010</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>메리로트</t>
+          <t>클리어 맥(Clear MAC)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2565,7 +5107,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>바이오디피씨(주)</t>
+          <t>(주)서흥헬스케어 2공장</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2575,19 +5117,19 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>산화아연, 니코틴산아미드, 구연산(무수), 스테아린산마그네슘, DL-사과산, 식물혼합추출농축분말, 이산화규소, 효소처리스테비아, 합성향료, 기타가공품, 파인애플농축, 자일리톨, 덱스트린, D-소비톨, 이소말트</t>
+          <t>차전자피식이섬유(고시형), 난소화성말토덱스트린(고시형), 이눌린/치커리추출물(고시형), 구아검가수분해물(고시형), 펙틴</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>구강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20250577120172</t>
+          <t>20180504061478</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,12 +5139,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20250577120</t>
+          <t>20180504061</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>유기농 고체레몬즙</t>
+          <t>파인애플주스농축액</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2612,17 +5154,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>주식회사 신비바이오</t>
+          <t>주식회사 웰런비앤에프 고창공장</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260704</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>가공유지, 과.채가공품</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2634,7 +5176,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>202606840485</t>
+          <t>20180504061479</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2644,84 +5186,4972 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20260684048</t>
+          <t>20180504061</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>대추칩</t>
+          <t>리포좀 연어이리추출물PDRN</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>호뜨락 농업법인 주식회사</t>
+          <t>주식회사 웰런비앤에프 고창공장</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260704</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>대추</t>
+          <t>정제수, 기타 수산물가공품, 레시틴, 구연산</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>피부</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>20180504061480</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>20180504061</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>파이토좀 연어이리추출물PDRN</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>주식회사 웰런비앤에프 고창공장</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>정제수, 기타 수산물가공품, 레시틴, 비타민C</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20180504061481</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>20180504061</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>하이포좀 연어이리추출물PDRN</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>주식회사 웰런비앤에프 고창공장</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>정제수, 기타 수산물가공품, 레시틴, 구연산, 시클로덱스트린, 전지분유</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20190413079322</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>20190413079</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>보리한잔</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>액상차</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>동원시스템즈 횡성사업장</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>정제수, 보리추출액, 맥아추출물분말, 탄산수소나트륨, 향료</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20190391582683</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>20190391582</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>올인원 파이토핏</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>(주)네추럴웨이 포천제2공장</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>검정콩분말, 수크랄로스, 마늘농축액, 양파추출농축분말, 효소처리스테비아, 연어이리추출물, 발효식초, 약모밀추출분말, 계피농축액, 치커리뿌리추출물, 건조서양자두농축액, 헛개나무과병추출분말, 생강농축액, 정제수, 시클로덱스트린액, 기타과당, 기타 농산가공품, 과.채가공품, 대추농축액, 서류가공품, 고구마농축분말, 녹차나무잎추출물분말, 호박농축분말, 과.채가공품, 매실농축액, 강황농축액, 레드자몽농축액, 딸기농축액, 향료, 브로콜리농축액, 양배추농축분말, 레드비트농축액, 레몬농축액, 오렌지농축액, 바나나농축분말, 토마토농축액, 키위농축액, 시금치추출물분말, 파인애플농축액, 삼백초추출물분말, 당근추출분말, 사과농축액, 배농축과즙, DL-사과산, 젖산칼슘, 인산, 포도농축액, 베리혼합농축액, 혼합제제</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20190391582682</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>20190391582</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>레드비트주스농축액</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>(주)네추럴웨이 포천제2공장</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>구연산(무수), 레드비트농축액</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2020019538599</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>20200195385</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>베노프x야곰이 단백질쉐이크 더블쿠앤크크런치</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>주식회사베노프하우스</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>수크랄로스, 효소처리스테비아, 기타소금, 유청단백분말, 코코아분말, 두류가공품, 혼합제제, 과자, 초콜릿가공품, 과자, 두류가공품, 분리유단백, 알룰로오스, 두류가공품</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>단백질</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2020039310948</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>20200393109</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>시원하게 마시는 도라지차</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>액상차</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>여주시 농업기술센터 농산물종합가공센터</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>도라지뿌리, 둥굴레뿌리, 정제수</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>면역</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2020042006896</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>20200420068</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>락토바실러스 플란타룸 LRCC 5193</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>주식회사 아이제이푸드</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>전분가공품, Lactiplantibacillus plantarum</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20200391559462</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>20200391559</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>파바빈프로테인</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>(주)성진바이오 제1공장</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>해바라기씨앗, 잠두씨앗</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2020053007624</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>20200530076</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>흑하랑상추복합발효추출물</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>액상차</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>농업회사법인주식회사유일식품</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>건조상추, 정제수, 쌀, 강황뿌리줄기, 보리</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2021029327894</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>20210293278</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>레인보우 미니구슬 푸드컬러 S</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>당류가공품</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>내츄럴팩토리 주식회사</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>캔디류, 가공유지, 치자청색소, 식품첨가물혼합제제, 식품첨가물혼합제제, 치자황색소, 식품첨가물혼합제제, 베리류색소, 식품첨가물</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>202102030783589</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>20210203078</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>덴티파이토18 구강유산균</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>당류가공품</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>채움바이오 주식회사</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>D-소비톨, 식품첨가물, 자일리톨, 혼합제제, 구아검가수분해물(고시형), 기타 농산가공품, 기타가공품, 기타가공품, 이산화규소, 스테아린산마그네슘, 프로바이오틱스(고시형)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>프로바이오틱스</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>202102030783590</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>20210203078</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>비고맥스</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>채움바이오 주식회사</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>과.채가공품, 이산화규소, 스테아린산마그네슘</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>202206834731193</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>20220683473</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>요 시크릿 가득 채운 크랜베리</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>고형차</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>주식회사 에이브바이오랩스</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>고형차</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>202206834731187</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>20220683473</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>소연골 콘드로이친 1200 트리플</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>고형차</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>주식회사 에이브바이오랩스</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>고형차, 식품첨가물</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>관절</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>202206834731207</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>20220683473</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>EA Alpha 복합물</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>고형차</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>주식회사 에이브바이오랩스</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>이눌린/치커리추출물(고시형), 포도당, 식품첨가물, 식품첨가물혼합제제, 기타가공품, 유청단백분말, 유함유가공품, 식품첨가물, 기타가공품, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>단백질</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>202206834731209</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>20220683473</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>산양삼 포뮬러</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>고형차</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>주식회사 에이브바이오랩스</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>식품첨가물, 식품첨가물혼합제제, 홍삼농축액(고시형), 땅콩 또는 견과류가공품, 기타가공품, 기타가공품, 이눌린/치커리추출물(고시형), 난소화성말토덱스트린(고시형), 식품첨가물, 덱스트린, 기타가공품, 기타 농산가공품, 기타가공품, 기타가공품, 과.채가공품, 기타가공품</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>에너지</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>202206834731191</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>20220683473</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>베르베린 리셋업</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>고형차</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>주식회사 에이브바이오랩스</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>고형차, 식품첨가물</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>혈당</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>202206834731205</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>20220683473</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>하스카프베리복합분말추출물</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>고형차</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>주식회사 에이브바이오랩스</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>과.채가공품, 덱스트린, 난소화성말토덱스트린(고시형), 식품첨가물, 고형차, 효모식품, 기타 농산가공품, 과.채가공품, 과.채가공품, 과.채가공품, 과.채가공품, 과.채가공품, 효모식품, 혼합제제, 식품첨가물</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2023052806085</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>20230528060</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>참송이버섯 분말</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>포천시농산물종합가공센터</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>송이자실체</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20230528144330</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>20230528144</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>메리로트</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>바이오디피씨(주)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>산화아연, 니코틴산아미드, 구연산(무수), 스테아린산마그네슘, DL-사과산, 식물혼합추출농축분말, 이산화규소, 효소처리스테비아, 합성향료, 기타가공품, 파인애플농축, 자일리톨, 덱스트린, D-소비톨, 이소말트</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>구강</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20230609874556</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>20230609874</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>아마씨추출분말</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>(주)뉴트리션바이오</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20230609874558</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>20230609874</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>블랙마카분말</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>(주)뉴트리션바이오</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>고형차</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20240365166262</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>20240365166</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>세인트마린 프리미엄 콜라겐</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>콜마비앤에이치(주)세종3공장</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>생선콜라겐</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20240365166263</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>20240365166</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>자보티카바 원데이 핏</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>콜마비앤에이치(주)세종3공장</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2024011872836</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>20240118728</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>망고정 망고파우더</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>당류가공품</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>마이베이스</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>설탕, 과.채가공품, 향료, 치자황색소, 분말유크림, 덱스트린</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2024011872841</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>20240118728</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>탐나는 다방커피파우더</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>당류가공품</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>마이베이스</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>백설탕, 식물성크림, 커피, 스테비텐후레쉬, 향료, 향료</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2024011872842</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>20240118728</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>돌우물 다방커피파우더</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>당류가공품</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>마이베이스</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>설탕, 식물성크림, 커피, 스테비텐후레쉬, 향료, 수크랄로스</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20250577120172</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>20250577120</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>유기농 고체레몬즙</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>주식회사 신비바이오</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>가공유지, 과.채가공품</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>202606840485</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>20260684048</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>대추칩</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>호뜨락 농업법인 주식회사</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>대추</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>202609353644</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>20260701</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>20260935364</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>매실농축액 EsteraHerb</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>액상차</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>리코셀바이오</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>20260702</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>차즈기, 계피, 매실</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>202601552408</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>20260155240</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>마늘후레이크</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>텅타이 주식회사</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>마늘, 콩기름(대두유)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026015524012</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>20260155240</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>간피키누</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>텅타이 주식회사</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>고추</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>19880607021528</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>19880607021</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>선망 티 포 베러라이프 콤부차 포도</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>고형차</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>(주)케이지앤에프</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>포도종자추출물, DL-사과산, 포도향분말, 홍차추출분말, 수크랄로스, 비타민C, 포도과즙분말, 포도향분말, 에리스리톨, 기타가공품, 탄산수소나트륨, 구연산, 유산균, 난소화성말토덱스트린(고시형), 프락토올리고당, 스테비올배당체, 포도과피, 과.채가공품, 치커리뿌리추출물</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>프로바이오틱스</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20020461222560</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>20020461222</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CGV 롱칠리스치즈스틱</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>DK냉동식품(주)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>콩기름(대두유), 팽창제제, 가공치즈, 기타가공품, 정제수, 기타가공품, 곡류가공품</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2003014126063</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>20030141260</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>고소하고 맛있는 볶은유부</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>한빛식품</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>가공두부, 간장</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20070435176367</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>20070435176</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>유산균브이V3사균체</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>(주)메디오젠 제천공장</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Ligilactobacillus salivarius, Limosilactobacillus fermentum, Lactiplantibacillus plantarum, 덱스트린</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>프로바이오틱스</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20090458111415</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>20090458111</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>식물성 OMEGA-3 젤리스틱 글루타치온 자몽</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>(주)화인에프티</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>혼합제제, 정제소금, 정제수, 레드자몽농축액, 덱스트린, 백설탕, 프락토올리고당, 결정과당, 액상과당, 들기름, 천연자몽향, 기타가공품, DL-사과산, 카제인나트륨, 아라비아검, 효소처리스테비아, 효모추출분말, 구연산(무수), 히비스커스꽃잎추출분말, 에리토브산나트륨, 비타민미네랄혼합제제</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20090458111411</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>20090458111</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>히비스커스차추출분말</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>고형차</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>(주)화인에프티</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>히비스커스꽃잎농축액, 덱스트린</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20100358177547</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>20100358177</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>안토시아닌-후코란 나노복합체 분말</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>주식회사 제이비케이랩</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>과.채가공품, 아로니아추출물분말</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20130345125505</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>20130345125</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>탑티어커피 피스타치오향 파우더</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>당류가공품</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>주식회사 컵풀</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>식물성크림혼합분말, 식물성크림, 설탕, 피스타치오향, 벌꿀분말, 정제소금, 피스타치오향, 이산화규소, 치자청색소, 식용색소황색제4호</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20150443219291</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>20150443219</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>하이스타M</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>(주)다인소재</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>염화칼륨, 트레할로스, 펙틴, 카라기난, 덱스트린, 잔탄검</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20180519145261</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>20180519145</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>베리베리 메론퓨레 무가당</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>(주)선인</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>멜론</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>20190456003372</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>20190456003</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>정성담은 보양침향환</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>농업회사법인주식회사에프앤비바이오</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>식물혼합분말, 사양벌꿀, 침향나무수지가침착된수간목분말, 글리세린, 대추농축액, 홍삼청, 녹용추출분말</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>에너지</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2019055809092</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>20190558090</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>오방낭자(五方囊子) 젤리스틱</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>캔디류</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>농업회사법인주식회사부성</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>대추농축액, 과당, 정제수, 혼합제제, 은행추출물, 홍삼농축액, 대추향</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>에너지</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>20190349087115</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>20190349087</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>하루전환</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>투더</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>질경이씨앗껍질분말, 호박, 비트루트분말, 강황뿌리줄기</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>20190349087116</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>20190349087</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>블랙빈환</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>투더</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>효모식품, 검정콩, 약모밀지상부, 차즈기</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>20190349087113</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>20190349087</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>강황환</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>투더</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>팽화미, 감귤껍질, 강황뿌리줄기</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>20190349087114</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>20190349087</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>헛개환</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>투더</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>헛개나무열매</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>20200424007794</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>20200424007</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>청양고추분말80</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>(주)신정에프앤비</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>덱스트린, 변성전분, 고춧가루</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2020037434987</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>20200374349</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>요아정 팝팝톡톡 딸기</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>당류가공품</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>주식회사 홈푸드</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>캔디류, 기타설탕, 가공유지, 혼합분유, 유당, 당류가공품, 혼합제제, 코치닐추출색소, 기타가공품, 향료</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>20200467503765</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>20200467503</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>사프란추출분말</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>올담식품</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>덱스트린, 사프란암술머리추출물</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>20210519071201</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>20210519071</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>디알에스 엔오부스터</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>엔피케이(주) 2공장</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>덱스트린, 타우린, 고형차</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>피로개선</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>20210606928228</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>20210606928</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>벌컥 배도라지즙</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>액상차</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>주식회사 마루바이오</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>도라지뿌리추출액, 배농축액, 사양벌꿀</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>면역</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>202102030783591</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>20210203078</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>파라다이스그레인컴플렉스</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>채움바이오 주식회사</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>과.채가공품, 기타 농산가공품, 기타가공품, 과.채가공품</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>20210396369248</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>20210396369</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>해궁비책 해마진</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>캔디류</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>주식회사 해나눔</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>기타가공품, 고형차, 기타가공품, 기타 수산물가공품, 결정셀룰로스, 덱스트린, 글리세린지방산에스테르, 판토텐산칼슘, 황산망간, 산화아연, 비타민B1염산염, 효모식품, 비타민B6염산염, 비타민B2, 이산화규소, 스테아린산마그네슘, 히드록시프로필메틸셀룰로스, 비타민C</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>20210396369247</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>20210396369</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>그린파이토 저포드 식이섬유정</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>주식회사 해나눔</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>크랜베리농축액분말, 라즈베리농축분말, 포도과즙분말, 파인애플과즙분말, 클로렐라, 토마토추출물분말, 레몬과즙분말, 올리브잎추출분말, 차전자피식이섬유(고시형), 호박추출물, 시금치추출물분말, 케일추출물분말, 기타 농산가공품, 난소화성말토덱스트린(고시형), 결정셀룰로스, 케르세틴, 상추추출물, 기타가공품, 서양박하잎추출분말, 유산균혼합분말, 결명자추출물분말, 이산화규소, 스테아린산마그네슘, 키위과즙, 블루베리농축분말, 천마추출분말, 바나나농축분말</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>항산화</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>20210617177373</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>20210617177</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>더 진한 6년근 홍삼정골드</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>액상차</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>채움에프앤비농업회사법인주식회사</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>홍삼추출액, 홍삼농축액, 홍삼청, 식물혼합농축액, 숙지황등혼합농축액, 올리고당가공품, 올리고당, 과당, 정제수</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>에너지</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2022060407966</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>20220604079</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>베리베리스틱</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>(주)원일바이오 제1공장</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>딸기과즙분말, 세븐베리농축분말</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>20220520237272</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>20220520237</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>파라다이스 그레인 블랜드 알파</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>당류가공품</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>주식회사 신영허브</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>과.채가공품, 식품첨가물, 기타 농산가공품, 유함유가공품, 이눌린/치커리추출물(고시형), 기타가공품, 과.채가공품, 기타가공품, 포도당</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>20220520237270</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>20220520237</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>파라다이스 그레인 프리미엄 알파</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>캔디류</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>주식회사 신영허브</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>당류가공품, 식품첨가물혼합제제, 결정셀룰로스, 스테아린산마그네슘, 이산화규소</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>202206834731214</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>20220683473</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>HA02복합물</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>고형차</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>주식회사 에이브바이오랩스</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>20260705</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>식품첨가물혼합제제, 식품첨가물, 기타가공품, 프로폴리스추출물(고시형), 식품첨가물혼합제제, 기타가공품, 과.채가공품, 식품첨가물, 혼합제제</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>202206834731197</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>20220683473</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>니어젠</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>고형차</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>주식회사 에이브바이오랩스</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>20260705</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>식품첨가물, 고형차</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>202206834731189</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>20220683473</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>시아넥스 맥스</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>고형차</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>주식회사 에이브바이오랩스</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>20260705</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>식품첨가물, 식품첨가물, 고형차</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>202206834731195</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>20220683473</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>안티라밋 알파</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>고형차</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>주식회사 에이브바이오랩스</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>20260705</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>식품첨가물, 고형차</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>202206834731213</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>20220683473</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>크랜베리 복합물</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>고형차</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>주식회사 에이브바이오랩스</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>과.채가공품, 이눌린/치커리추출물(고시형), 식품첨가물, 과.채가공품, 과.채가공품, 과.채가공품, 과.채가공품</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>202206834731211</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>20220683473</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>서리태복합물</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>고형차</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>주식회사 에이브바이오랩스</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>기타가공품, 식품첨가물, 기타가공품, 기타가공품, 포도당, 덱스트린, 식품첨가물, 기타가공품, 기타가공품, 효모식품, 식품첨가물, 효소식품, 식품첨가물, 식품첨가물, 기타가공품, 혼합제제, 식품첨가물, 식품첨가물</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>20230528144325</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>20230528144</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>밤 한잔</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>고형차</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>바이오디피씨(주)</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>피스타치오견과분말, 캐모마일추출물분말, 체리농축분말, 산화마그네슘, 글리신, 테아닌, 인공캐모마일향, 프락토올리고당, 레몬향분말, 이산화규소, 가바, 레몬밤추출물, L-트립토판, 해조칼슘, 이노시톨, 엽산, 산화아연</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>수면</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>20230612332315</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>20230612332</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>카무트 브랜드밀 리얼 효소 골드</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>효소식품</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>(주)웰레스트</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>당류가공품, 식물성크림, 덱스트린, 밤향, 이산화규소, 효소처리스테비아, 당류가공품, 농축유청, 분리대두단백, 이눌린/치커리추출물(고시형), 포도당, 효소식품, 효소식품, 효소식품, 프락토올리고당</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>효소</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2023043187024</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>20230431870</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>보라 프리믹스</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>팜앤브로주식회사2공장</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>정제소금, 자색고구마가루, 멥쌀가루, 찹쌀분말</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2023043187025</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>20230431870</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>빨강 프리믹스</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>팜앤브로주식회사2공장</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>멥쌀가루, 찹쌀분말, 홍국쌀, 정제소금</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2023043187021</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>20230431870</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>흰색 프리믹스</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>팜앤브로주식회사2공장</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>정제소금, 찹쌀분말, 멥쌀가루</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2023043187022</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>20230431870</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>노랑 프리믹스</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>팜앤브로주식회사2공장</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>정제소금, 호박가루, 찹쌀분말, 멥쌀가루</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2023043187023</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>20230431870</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>초록 프리믹스</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>팜앤브로주식회사2공장</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>쑥가루, 멥쌀가루, 찹쌀분말, 정제소금</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>20230609874559</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>20230609874</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>웰컴웰키 말토인 샐러드 파우더</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>(주)뉴트리션바이오</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>산화아연, 프로바이오틱스(고시형), 피로인산제이철, 두류가공품, 과.채가공품, 기타가공품, 비타민C, 산화마그네슘, 과.채가공품, 유함유가공품, 복합조미식품, 기타가공품, 난소화성말토덱스트린(고시형), 이눌린/치커리추출물(고시형), 식품첨가물혼합제제</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2024071601092</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>20240716010</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>배터믹스(빠삭)</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>주식회사 SL푸드원 생태산업단지 3공장</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>곡류가공품, 전분, 전분, 밀가루, 곡류가공품, 변성전분, 곡류가공품, 정제소금, 변성전분, 설탕, 식품첨가물, 식품첨가물</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2024092410715</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>20240924107</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>유기농 컬리너리 말차</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>고형차</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>마이크로파우더</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>건조녹차</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>20240672181108</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>20240672181</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>블랙마카 맥스포스</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>고형차</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>(주)씨이에스팜</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>마카뿌리, L-아르지닌, 포도당, 비수리추출분말, 흑마늘분말, 스테아린산마그네슘, 타우린, 산화아연, 산화마그네슘, 대나무수액, 치커리뿌리추출물, 자라분말</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>남성건강</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>20240672181109</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>20240672181</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>알파민씨정</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>(주)씨이에스팜</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>혼합제제, 생선콜라겐, 브로콜리추출물, 효소식품, 회화나무열매추출분말, 강황추출물분말, 양배추추출액분말, 효모식품, 기타가공품, 스테아린산마그네슘, 이산화규소, 녹차추출물, α-시클로덱스트린</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>항산화</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2025074213120</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>20250742131</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>JAYU 메론연유크림</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>당류가공품</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>(주)소이프트바이옴 제3공장</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>당류가공품, 메론레진, 향료, 식물성크림, 변성전분, 구아검</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026020310812</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>20260203108</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>세척잔파 슬라이스</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>성오유통(주)</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>잔파</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>202606510503</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>20260651050</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>김치TOK 토핑</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>뉴벡</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>기타가공품, 기타가공품, 동결건조대파, 동결건조양파</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>20010415034798</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>20010415034</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>색고드름캔디</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>캔디류</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>국제제과(주)</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>설탕, 물엿, 딸기과립, 레몬과립, 포도과립, 향료, 향료, 향료, 향료, 향료, 산도조절제, 산도조절제, 혼합제제, 옥수수전분, 가공유지, 포도농축액, 딸기농축액, 레몬농축액, 유화제, 혼합제제, 정제수</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>20050372172795</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>20050372172</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>바노 식물성 멜라토닌 2mg 함유</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>(주)허브큐어</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>산화아연, 기타가공품, 과.채가공품, 혼합제제, 해조칼슘, 유청칼슘, 비타민B6염산염, 가공유지, 니코틴산아미드, 히드록시프로필메틸셀룰로스, 기타 농산가공품, 글리세린지방산에스테르, 이눌린/치커리추출물(고시형), 옥수수전분, L-트립토판, 테아닌, 산화마그네슘, 결정셀룰로스, 기타 농산가공품</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>수면</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>20050372172794</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>20050372172</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>바노 식물성 멜라토닌 5mg 함유</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>(주)허브큐어</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>산화아연, 기타가공품, 과.채가공품, 혼합제제, 해조칼슘, 유청칼슘, 비타민B6염산염, 가공유지, 니코틴산아미드, 기타 농산가공품, 글리세린지방산에스테르, 이눌린/치커리추출물(고시형), 옥수수전분, L-트립토판, 테아닌, 산화마그네슘, 결정셀룰로스, 기타 농산가공품, 히드록시프로필메틸셀룰로스</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>수면</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>20060415215382</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>20060415215</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>올리브유연질캡슐</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>올리브유</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>주식회사 노바렉스 2공장</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>덱스트린, 카라기난, 글리세린, 변성전분, 정제수, 올리브유</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>20070435069963</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>20070435069</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>칠년근 산삼환</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>농업법인(주)옻가네</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>벌꿀, 침향나무수지가침착된수간목, 인삼뿌리, 참당귀뿌리, 작약뿌리, 천궁뿌리줄기, 지황포제가공한뿌리, 인삼뿌리, 녹용</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>에너지</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>20070435069964</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>20070435069</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>통째로 칠년근 산삼환</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>농업법인(주)옻가네</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>벌꿀, 침향나무수지가침착된수간목, 인삼뿌리, 참당귀뿌리, 작약뿌리, 천궁뿌리줄기, 지황포제가공한뿌리, 인삼뿌리, 녹용</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>에너지</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>20070467207136</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>20070467207</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>아침마당 인보샷 GIN</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>액상차</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>주식회사 금산몰</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>식물혼합추출물, 알룰로오스, 사양벌꿀, 레몬농축액, 모과농축액, 폴리덱스트로스, 홍삼농축액, 타우린, 자몽종자추출물, 비타민B2</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>에너지</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>20100515088787</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>20100515088</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>테라큐민 액티브 SOD효소</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>효소식품</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>엔피케이(주)</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>이소말트, 결정과당, 알파현미분말, 효소식품, 심황색소, 기타가공품, 파인애플추출분말, 유산균혼합분말, Clostridium butyricum strain Miyairi, 케일분말, 기타 식용유지가공품, 감자추출물분말, 효소식품, 아티초크추출분말, 대나무잎추출물, 파파야추출분말, 백태분말, 전지분유</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>효소</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>201102571531694</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>20110257153</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>핫허니</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>당류가공품</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>다솔푸드테크 주식회사</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>향료, 벌꿀, 소스, 소브산칼륨, 카라멜색소 Ⅳ</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>20120383884192</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>20120383884</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>코편숨H</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>액상차</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>(주)만종바이오</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>20260705</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>칡뿌리, 산수유열매, 감귤껍질, 사삼뿌리, 모과, 뽕나무뿌리껍질, 도라지뿌리, 계피가지, 은행나무견과, 겨자씨앗, 무씨앗, 차즈기씨앗, 배초향지상부, 건조차즈기잎, 황기, 건조약모밀지상부, 마뿌리, 감초, 생강, 건지황, 대추, 오미자열매, 작약뿌리, 삽주뿌리줄기박, 천궁뿌리줄기, 복령균핵, 볶은도두어린꼬투리(연한,부풀기전), 왕느릅나무껍질, 배암차즈기분말, 케르세틴, 파인애플추출농축분말, l-멘톨, 이소말토올리고당, 변성전분, 정제수</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>항산화</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2013055814479</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>20130558144</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>두레효소</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>액상차</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>농업회사법인 문경미소 주식회사</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>오미자청, 양파발효액</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>효소</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>20170433005519</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>20170433005</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>샤인머스켓퓨레</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>주식회사 산지</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>비타민C, 과.채가공품</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2018042401941</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>20180424019</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>IQF 얼갈이</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>(농)농가생활협동조합</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>천일염, 배추</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2018042401939</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>20180424019</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>IQF 근대</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>(농)농가생활협동조합</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>천일염, 근대잎</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2018042401938</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>20180424019</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>IQF 시금치</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>(농)농가생활협동조합</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>천일염, 시금치</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>20200559283201</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>20200559283</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>자라다환</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>농업회사법인(주)동서건강</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>국화꽃, 천마뿌리, 산수유열매, 녹용, 중국당귀뿌리, 삼씨앗, 사양벌꿀</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>20200559283200</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>20200559283</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>당로하</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>액상차</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>농업회사법인(주)동서건강</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>소스, 바나바잎추출물, 액상차, 정제수</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>혈당</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2021061403263</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>20210614032</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>PLUM SYRUP by MESHIL</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>액상차</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>슬로푸드 주식회사 농업회사법인</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>정제수, 매실향, 카라멜색소 Ⅲ, 구연산, 감식초, 설탕, 매실농축액</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>20210519071202</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>20210519071</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>프롬파이토 차즈기 빌베리 촉촉젤리</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>엔피케이(주) 2공장</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Clostridium butyricum strain Miyairi, 원지추출액, 복령추출물분말, 효소처리스테비아, 미르틸루스산앵도농축분말, 혼합제제, 자일리톨, 블루베리향, 용설란시럽, 차즈기잎추출분말, 시클로덱스트린액, 과당, 블루베리농축액, 정제수, 구연산(무수), 기타 농산가공품, 글루코만난, 구연산삼나트륨, 블루베리농축분말, 아로니아농축분말, 결명자추출물분말, 전분가공품, β-시클로덱스트린, 열대과일혼합농축액</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>항산화</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>20210036719242</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>20210036719</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>메디포뮬러 산양유단백질</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>(주)비에스에프코리아</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>기타가공품, 식품첨가물, 정제소금, 혼합제제, 기타가공품, 기타가공품, 식품첨가물, 프락토올리고당, 혼합제제, 유함유가공품, 기타가공품, 유함유가공품, 식물성크림, 유함유가공품, 혼합분유, 유청단백분말</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>단백질</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>20220520237273</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>20220520237</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>파라다이스 그레인 라이트</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>캔디류</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>주식회사 신영허브</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>결정셀룰로스, 당류가공품, 이산화규소, 스테아린산마그네슘, 식품첨가물혼합제제</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>20220520237274</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>20220520237</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>올데이 파라다이스 그레인 라이트 탭</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>당류가공품</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>주식회사 신영허브</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>포도당, 기타가공품, 과.채가공품, 기타가공품, 이눌린/치커리추출물(고시형), 기타 농산가공품, 유함유가공품, 식품첨가물, 과.채가공품</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>20240203422189</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>20240203422</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>바로멜라</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>캔디류</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>주식회사 미쁨생활건강</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>20260704</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>기타가공품, 기타가공품, 히드록시프로필메틸셀룰로스, 이소말트, 포도당, 피스타치오견과분말, L-테아닌(고시형), 산화마그네슘, 스테아린산마그네슘, 비타민C, 이산화규소, 난소화성말토덱스트린(고시형), 레몬밤분말, 치커리추출분말, 기타가공품, 캐모마일추출물분말, 판토텐산칼슘, 녹차추출물분말(고시형), 구연산(무수), 이.디.티.에이.칼슘이나트륨, 비타민B1염산염, 산화아연</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>수면</t>
         </is>
       </c>
     </row>
@@ -3381,34 +10811,34 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="7" t="n">
-        <v>0</v>
+      <c r="D9" s="9" t="n">
+        <v>9</v>
       </c>
       <c r="E9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K9" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="L9" s="9" t="n">
         <v>1</v>
@@ -3422,35 +10852,35 @@
       <c r="O9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P9" s="7" t="n">
-        <v>0</v>
+      <c r="P9" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Q9" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="7" t="n">
-        <v>0</v>
+      <c r="R9" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="S9" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="U9" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="V9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="V9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="X9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="8" t="n">
-        <v>12</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -4344,19 +11774,19 @@
         </is>
       </c>
       <c r="B25" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>0</v>
@@ -4368,37 +11798,37 @@
         <v>0</v>
       </c>
       <c r="J25" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N25" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="K25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="S25" s="9" t="n">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="T25" s="8" t="n">
-        <v>30</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26">

--- a/output/2026-07_품목신고보고현황.xlsx
+++ b/output/2026-07_품목신고보고현황.xlsx
@@ -1602,7 +1602,6 @@
           <t>20260702</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>기타</t>
@@ -1739,7 +1738,6 @@
           <t>20260702</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>면역</t>
@@ -2017,7 +2015,6 @@
           <t>20260702</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>기타</t>
@@ -2295,7 +2292,6 @@
           <t>20260702</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>기타</t>
@@ -4280,61 +4276,61 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E24" s="9" t="n">
         <v>41</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I24" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="L24" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="M24" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="N24" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="O24" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="P24" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q24" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="J24" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="K24" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="L24" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="M24" s="9" t="n">
-        <v>57</v>
-      </c>
-      <c r="N24" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="O24" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="P24" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q24" s="9" t="n">
-        <v>10</v>
-      </c>
       <c r="R24" s="9" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="S24" s="9" t="n">
-        <v>1334</v>
+        <v>1206</v>
       </c>
       <c r="T24" s="8" t="n">
-        <v>1948</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="25">
